--- a/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P108_pos_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
+++ b/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P108_pos_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5406411408100804</v>
+        <v>0.4723758197465214</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5441741798208495</v>
+        <v>0.6802914711424632</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5406411408100804</v>
+        <v>0.4723758197465214</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5441741798208495</v>
+        <v>0.6802914711424632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4603038401756906</v>
+        <v>0.5318079865984078</v>
       </c>
       <c r="F2" t="n">
-        <v>0.508019239006987</v>
+        <v>0.714111827317133</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9976499635433266</v>
+        <v>0.9973142329693742</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9973416212698993</v>
+        <v>0.9985738856547363</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5133159268929504</v>
+        <v>0.6963446475195822</v>
       </c>
     </row>
   </sheetData>
